--- a/data/extracted/inventory-receipts/Rep CONTENEDOR INTERLOCK ROLLO IVORY +.XLSX
+++ b/data/extracted/inventory-receipts/Rep CONTENEDOR INTERLOCK ROLLO IVORY +.XLSX
@@ -1,18 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AF0036-DESKTOP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\txpacifico\txp-inventory\data\extracted\inventory-receipts\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD5FA76-587E-451E-90E2-9F8CA1C6F000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10080" windowHeight="9465"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="IBUM" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -209,7 +211,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###,###,###,###,##0.#0"/>
   </numFmts>
@@ -250,12 +252,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -535,50 +536,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
-    <col min="8" max="12" width="10.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
+    <col min="8" max="12" width="10.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -616,12 +617,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -659,7 +660,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -697,7 +698,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -735,7 +736,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -773,7 +774,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -811,7 +812,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -849,7 +850,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -887,7 +888,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -925,7 +926,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -963,7 +964,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -1001,7 +1002,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -1039,7 +1040,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -1077,7 +1078,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
@@ -1115,7 +1116,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -1153,7 +1154,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -1191,7 +1192,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
@@ -1229,7 +1230,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F23" s="1" t="s">
         <v>57</v>
       </c>
@@ -1249,7 +1250,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F24" s="1" t="s">
         <v>21</v>
       </c>
@@ -1269,7 +1270,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F25" s="1" t="s">
         <v>57</v>
       </c>
@@ -1289,7 +1290,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1309,7 +1310,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F27" s="1" t="s">
         <v>57</v>
       </c>
@@ -1329,7 +1330,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F28" s="1" t="s">
         <v>21</v>
       </c>
@@ -1349,7 +1350,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F29" s="1" t="s">
         <v>57</v>
       </c>
@@ -1373,4 +1374,19 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D6AF0F0-A480-4E0F-8B5B-B9BD94847FEF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>47328</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>